--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487448_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487448_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4574</v>
+        <v>5.0189</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9925</v>
+        <v>3.2332</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4649</v>
+        <v>1.7857</v>
       </c>
       <c r="G2" t="n">
         <v>6.5337</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>0.729</v>
+        <v>0.2905</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7575</v>
+        <v>-0.0018</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0285</v>
+        <v>0.2923</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8260999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2319</v>
+        <v>2.5507</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0918</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1401</v>
+        <v>1.7659</v>
       </c>
       <c r="G3" t="n">
         <v>1.5341</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9144</v>
+        <v>0.2332</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4317</v>
+        <v>0.1247</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4828</v>
+        <v>0.1085</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7834</v>
+        <v>2.5207</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0797</v>
+        <v>2.9774</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2963</v>
+        <v>-0.4567</v>
       </c>
       <c r="G4" t="n">
         <v>4.0194</v>
@@ -766,13 +766,13 @@
         <v>2.3502</v>
       </c>
       <c r="S4" t="n">
-        <v>0.113</v>
+        <v>-0.1497</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1029</v>
+        <v>-0.2053</v>
       </c>
       <c r="U4" t="n">
-        <v>0.216</v>
+        <v>0.0556</v>
       </c>
       <c r="V4" t="n">
         <v>0.2178</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.054</v>
+        <v>0.075</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1958</v>
+        <v>-0.0935</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1418</v>
+        <v>0.1685</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1313</v>
@@ -844,13 +844,13 @@
         <v>0.1958</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0772</v>
+        <v>0.2063</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.1023</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0772</v>
+        <v>0.104</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. REY CONDE</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7794</v>
+        <v>-1.6809</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7806</v>
+        <v>-1.7986</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9988</v>
+        <v>0.1177</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4649</v>
+        <v>-0.2249</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1569</v>
+        <v>-2.2765</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6218</v>
+        <v>2.0515</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6618000000000001</v>
+        <v>0.1522</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0204</v>
+        <v>-1.8734</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6822</v>
+        <v>2.0256</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8031</v>
+        <v>-0.3771</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1364</v>
+        <v>-0.4031</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9396</v>
+        <v>0.026</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1958</v>
+        <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5103</v>
+        <v>0.7019</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1188</v>
+        <v>0.2611</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3915</v>
+        <v>0.4408</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>Y. REY CONDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0915</v>
+        <v>-1.7527</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3697</v>
+        <v>-0.7806</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2781</v>
+        <v>-0.9721</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2249</v>
+        <v>-1.4649</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2765</v>
+        <v>0.1569</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0515</v>
+        <v>-1.6218</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1522</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8734</v>
+        <v>0.0204</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0256</v>
+        <v>-0.6822</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3771</v>
+        <v>-0.8031</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4031</v>
+        <v>0.1364</v>
       </c>
       <c r="O7" t="n">
-        <v>0.026</v>
+        <v>-0.9396</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1543</v>
+        <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2912</v>
+        <v>-0.4836</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.31</v>
+        <v>-0.1188</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6012</v>
+        <v>-0.3648</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1578</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ TAPIA</t>
+          <t>Q. HUANG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8115</v>
+        <v>-2.461</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.755</v>
+        <v>-3.4249</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0564</v>
+        <v>0.9639</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.52</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.4502</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7786</v>
+        <v>-0.0604</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2523</v>
+        <v>-0.8647</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5393</v>
+        <v>-0.3845</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.713</v>
+        <v>-0.4802</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2677</v>
+        <v>0.3541</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2021</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0656</v>
+        <v>0.4197</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9792</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1751</v>
+        <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6878</v>
+        <v>0.3042</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6516</v>
+        <v>-0.4058</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0362</v>
+        <v>0.71</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q. HUANG</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9076</v>
+        <v>-2.586</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7913</v>
+        <v>-1.4182</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8837</v>
+        <v>-1.1678</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-0.8819</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4502</v>
+        <v>-0.0687</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0604</v>
+        <v>-0.8131</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8647</v>
+        <v>1.1243</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3845</v>
+        <v>0.4729</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4802</v>
+        <v>0.6515</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3541</v>
+        <v>-2.0062</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.5416</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4197</v>
+        <v>-1.4646</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3709</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1543</v>
+        <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7834</v>
+        <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1424</v>
+        <v>-0.8411999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7722</v>
+        <v>-0.584</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6298</v>
+        <v>-0.2572</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8837</v>
+        <v>-0.2754</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8837</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>S. RODRÍGUEZ TAPIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0266</v>
+        <v>-3.3348</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7252</v>
+        <v>-3.412</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3014</v>
+        <v>0.0772</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8819</v>
+        <v>-2.52</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0687</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8131</v>
+        <v>-1.7786</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1243</v>
+        <v>-1.2523</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4729</v>
+        <v>-0.5393</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6515</v>
+        <v>-0.713</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0062</v>
+        <v>-1.2677</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5416</v>
+        <v>-0.2021</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4646</v>
+        <v>-1.0656</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5875</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9585</v>
+        <v>-2.1543</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2818</v>
+        <v>0.1645</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.891</v>
+        <v>-0.0053</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3908</v>
+        <v>0.1698</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2024</v>
+        <v>-4.4533</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5997</v>
+        <v>-1.8239</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6027</v>
+        <v>-2.6294</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5208</v>
@@ -1312,13 +1312,13 @@
         <v>2.546</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5605</v>
+        <v>-0.8115</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0516</v>
+        <v>-0.2758</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5089</v>
+        <v>-0.5356</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7086</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.400300000000001</v>
+        <v>-6.103399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.0533</v>
+        <v>-5.7563</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.347</v>
+        <v>-0.3471000000000002</v>
       </c>
       <c r="G12" t="n">
         <v>4.832800000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>8.8484</v>
+        <v>8.848399999999998</v>
       </c>
       <c r="I12" t="n">
         <v>-4.0156</v>
@@ -1390,13 +1390,13 @@
         <v>14.6884</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6824000000000001</v>
+        <v>-0.3854</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4057</v>
+        <v>-1.1087</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7234999999999999</v>
+        <v>0.7233999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-6.6338</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.94</v>
+        <v>4.7311</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4797</v>
+        <v>2.5354</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4603</v>
+        <v>2.1958</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5339</v>
@@ -1468,13 +1468,13 @@
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3944</v>
+        <v>1.1855</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4784</v>
+        <v>0.534</v>
       </c>
       <c r="U13" t="n">
-        <v>0.916</v>
+        <v>0.6515</v>
       </c>
       <c r="V13" t="n">
         <v>2.7086</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3205</v>
+        <v>1.9399</v>
       </c>
       <c r="E14" t="n">
-        <v>1.823</v>
+        <v>2.0277</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4975</v>
+        <v>-0.0878</v>
       </c>
       <c r="G14" t="n">
         <v>1.4915</v>
@@ -1546,13 +1546,13 @@
         <v>2.1543</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2415</v>
+        <v>0.8609</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0047</v>
+        <v>0.2094</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2368</v>
+        <v>0.6515</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6083</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5749</v>
+        <v>1.7887</v>
       </c>
       <c r="E15" t="n">
         <v>0.8384</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7365</v>
+        <v>0.9503</v>
       </c>
       <c r="G15" t="n">
         <v>-0.09</v>
@@ -1624,13 +1624,13 @@
         <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4515</v>
+        <v>-0.2376</v>
       </c>
       <c r="T15" t="n">
         <v>-0.3694</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.1317</v>
       </c>
       <c r="V15" t="n">
         <v>0.9412</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. BARTOLOME COBLE</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6886</v>
+        <v>1.5658</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1338</v>
+        <v>-0.7696</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4451</v>
+        <v>2.3355</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.165</v>
+        <v>0.988</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6499</v>
+        <v>-1.0476</v>
       </c>
       <c r="I16" t="n">
-        <v>0.485</v>
+        <v>2.0356</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9245</v>
+        <v>0.7672</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5052</v>
+        <v>-0.3029</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4193</v>
+        <v>1.0701</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0895</v>
+        <v>0.2208</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1551</v>
+        <v>-0.7447</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9344</v>
+        <v>0.9655</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5668</v>
+        <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3616</v>
+        <v>-0.3219</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2841</v>
+        <v>-0.5576</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0776</v>
+        <v>0.2357</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8837</v>
+        <v>-0.2754</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6771</v>
+        <v>0.8316</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2813</v>
+        <v>-0.3762</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9584</v>
+        <v>1.2078</v>
       </c>
       <c r="G17" t="n">
-        <v>0.988</v>
+        <v>0.0028</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0476</v>
+        <v>-1.2045</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0356</v>
+        <v>1.2073</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7672</v>
+        <v>0.333</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3029</v>
+        <v>-0.3233</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0701</v>
+        <v>0.6563</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2208</v>
+        <v>-0.3302</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7447</v>
+        <v>-0.8812</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9655</v>
+        <v>0.551</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1751</v>
+        <v>0.3917</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1543</v>
+        <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2106</v>
+        <v>0.1617</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0692</v>
+        <v>-0.0053</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1413</v>
+        <v>0.167</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2754</v>
+        <v>0.2754</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>M. BARTOLOME COBLE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3666</v>
+        <v>0.6665</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3105</v>
+        <v>1.0314</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6771</v>
+        <v>-0.3649</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2191</v>
+        <v>-0.165</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1806</v>
+        <v>-0.6499</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3997</v>
+        <v>0.485</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8899</v>
+        <v>1.9245</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0412</v>
+        <v>0.5052</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8487</v>
+        <v>1.4193</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6708</v>
+        <v>-2.0895</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2218</v>
+        <v>-1.1551</v>
       </c>
       <c r="O18" t="n">
-        <v>0.551</v>
+        <v>-0.9344</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3502</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R18" t="n">
         <v>1.5668</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0058</v>
+        <v>0.3395</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2247</v>
+        <v>0.1817</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2189</v>
+        <v>0.1578</v>
       </c>
       <c r="V18" t="n">
-        <v>1.492</v>
+        <v>0.8837</v>
       </c>
       <c r="W18" t="n">
-        <v>1.492</v>
+        <v>0.8837</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0304</v>
+        <v>0.6634</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8879</v>
+        <v>-0.3105</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8575</v>
+        <v>0.9739</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0028</v>
+        <v>1.2191</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2045</v>
+        <v>-0.1806</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2073</v>
+        <v>1.3997</v>
       </c>
       <c r="J19" t="n">
-        <v>0.333</v>
+        <v>1.8899</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3233</v>
+        <v>1.0412</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6563</v>
+        <v>0.8487</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3302</v>
+        <v>-0.6708</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8812</v>
+        <v>-1.2218</v>
       </c>
       <c r="O19" t="n">
         <v>0.551</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3917</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7002</v>
+        <v>0.3026</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.517</v>
+        <v>0.2247</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1833</v>
+        <v>0.0779</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2754</v>
+        <v>1.492</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2754</v>
+        <v>1.492</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0246</v>
+        <v>-0.784</v>
       </c>
       <c r="E20" t="n">
         <v>-0.6006</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4239</v>
+        <v>-0.1833</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5878</v>
@@ -2014,13 +2014,13 @@
         <v>2.1543</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6118</v>
+        <v>-0.3713</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2506</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3613</v>
+        <v>-0.1207</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MIRANDA GARCIA</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2664</v>
+        <v>-1.0476</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7222</v>
+        <v>-0.1894</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5443</v>
+        <v>-0.8582</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1595</v>
+        <v>-1.7357</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2096</v>
+        <v>0.3158</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9499</v>
+        <v>-2.0515</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.621</v>
+        <v>0.3486</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0612</v>
+        <v>1.0616</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6822</v>
+        <v>-0.713</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5385</v>
+        <v>-2.0843</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2708</v>
+        <v>-0.7458</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2677</v>
+        <v>-1.3385</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1958</v>
+        <v>1.3709</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3028</v>
+        <v>-0.3119</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1012</v>
+        <v>-0.167</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2016</v>
+        <v>-0.1448</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>A. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6975</v>
+        <v>-1.0572</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5987</v>
+        <v>-0.6198</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0988</v>
+        <v>-0.4374</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7357</v>
+        <v>-1.1595</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3158</v>
+        <v>-0.2096</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0515</v>
+        <v>-0.9499</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3486</v>
+        <v>-0.621</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0616</v>
+        <v>0.0612</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.713</v>
+        <v>-0.6822</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0843</v>
+        <v>-0.5385</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7458</v>
+        <v>-0.2708</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3385</v>
+        <v>-0.2677</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9618</v>
+        <v>-0.0935</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5764</v>
+        <v>0.0012</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3854</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1487</v>
+        <v>-2.2159</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5268</v>
+        <v>-3.2198</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3781</v>
+        <v>1.0039</v>
       </c>
       <c r="G23" t="n">
         <v>-3.2621</v>
@@ -2248,13 +2248,13 @@
         <v>1.5668</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0825</v>
+        <v>-0.1497</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8316</v>
+        <v>-0.5246</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7492</v>
+        <v>0.3749</v>
       </c>
       <c r="V23" t="n">
         <v>0.6083</v>
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.400100000000002</v>
+        <v>7.0823</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3468999999999984</v>
+        <v>0.3470000000000009</v>
       </c>
       <c r="F24" t="n">
-        <v>6.053300000000001</v>
+        <v>6.7356</v>
       </c>
       <c r="G24" t="n">
         <v>-4.8326</v>
       </c>
       <c r="H24" t="n">
-        <v>-8.848300000000002</v>
+        <v>-8.8483</v>
       </c>
       <c r="I24" t="n">
-        <v>4.015799999999999</v>
+        <v>4.0158</v>
       </c>
       <c r="J24" t="n">
         <v>6.864899999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9845</v>
+        <v>0.9844999999999998</v>
       </c>
       <c r="L24" t="n">
         <v>5.880500000000001</v>
@@ -2311,13 +2311,13 @@
         <v>-11.6975</v>
       </c>
       <c r="N24" t="n">
-        <v>-9.832499999999998</v>
+        <v>-9.8325</v>
       </c>
       <c r="O24" t="n">
         <v>-1.865</v>
       </c>
       <c r="P24" t="n">
-        <v>3.916800000000001</v>
+        <v>3.9168</v>
       </c>
       <c r="Q24" t="n">
         <v>-14.6884</v>
@@ -2326,13 +2326,13 @@
         <v>18.6054</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6821000000000004</v>
+        <v>1.364300000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7234999999999997</v>
+        <v>-0.7234999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4057</v>
+        <v>2.0878</v>
       </c>
       <c r="V24" t="n">
         <v>6.6338</v>
